--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93416</v>
+        <v>93419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93392</v>
+        <v>93395</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93394</v>
+        <v>93397</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93419</v>
+        <v>93420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93395</v>
+        <v>93396</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93420</v>
+        <v>93425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93396</v>
+        <v>93401</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93398</v>
+        <v>93403</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93401</v>
+        <v>93403</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93403</v>
+        <v>93405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 63663-2025 artfynd.xlsx
+++ b/artfynd/A 63663-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136382139</v>
       </c>
       <c r="B2" t="n">
-        <v>93429</v>
+        <v>93431</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2170,7 +2170,7 @@
         <v>136379574</v>
       </c>
       <c r="B15" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>136379908</v>
       </c>
       <c r="B16" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>136380663</v>
       </c>
       <c r="B17" t="n">
-        <v>93405</v>
+        <v>93407</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>136379397</v>
       </c>
       <c r="B41" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,7 +5223,7 @@
         <v>136379836</v>
       </c>
       <c r="B42" t="n">
-        <v>93407</v>
+        <v>93409</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -7284,7 +7284,7 @@
         <v>136379494</v>
       </c>
       <c r="B60" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7395,7 +7395,7 @@
         <v>136379725</v>
       </c>
       <c r="B61" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>136380175</v>
       </c>
       <c r="B62" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
         <v>136380321</v>
       </c>
       <c r="B63" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7728,7 +7728,7 @@
         <v>136380437</v>
       </c>
       <c r="B64" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>136380929</v>
       </c>
       <c r="B65" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>136380989</v>
       </c>
       <c r="B66" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8672,7 +8672,7 @@
         <v>136379701</v>
       </c>
       <c r="B72" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
